--- a/capabilities/marginal-analysis/model.xlsx
+++ b/capabilities/marginal-analysis/model.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Inputs" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Labor &amp; Cost" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Allocation" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Checks" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Labor &amp; Cost" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Allocation" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="Season_Weeks">Inputs!$B$4</definedName>
@@ -708,8 +708,9 @@
           <t>Farmer_Hourly_Rate</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
-        <v>34.72</v>
+      <c r="B6" s="6">
+        <f>50000/1440</f>
+        <v/>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
@@ -756,8 +757,9 @@
           <t>Temp_Hourly_Rate</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n">
-        <v>17.36</v>
+      <c r="B8" s="6">
+        <f>25000/1440</f>
+        <v/>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -4179,7 +4181,7 @@
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>42768.32825620536</v>
+        <v>42761.66</v>
       </c>
       <c r="C11" s="10">
         <f>Profit</f>
@@ -4204,7 +4206,7 @@
         <v/>
       </c>
       <c r="D12" s="20">
-        <f>IF(ABS(C12-B12)&lt;=10,"PASS","FAIL")</f>
+        <f>IF(ABS(C12-B12)&lt;=0.5,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
